--- a/Normalisasi_SalesDB_Muaafii.xlsx
+++ b/Normalisasi_SalesDB_Muaafii.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muaafii Putra R\Documents\Kerja\MII-Maganghub\github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muaafii Putra R\Documents\Kerja\MII-Maganghub\github\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69F1C91F-057B-43B3-A7A0-CFD1F032DEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5157BF-EAE1-4E69-AFB7-ED1D52C435BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
     <sheet name="1_UNF" sheetId="2" r:id="rId2"/>
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
-    <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
-    <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
+    <sheet name="4_3NF" sheetId="5" r:id="rId4"/>
+    <sheet name="3_2NF" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -85,8 +85,60 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
+    <comment ref="P13" authorId="0" shapeId="0" xr:uid="{49AF41A4-D77F-41C7-B3C0-84CBD8FA59F7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{85114E98-82BF-4857-8C83-B4FA38715303}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G24" authorId="0" shapeId="0" xr:uid="{804FE793-AD9B-4865-9941-59B42DA863A1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="157">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -562,6 +614,58 @@
   </si>
   <si>
     <t xml:space="preserve">C --&gt; D; G --&gt; H; I --&gt; J; A --&gt; B; </t>
+  </si>
+  <si>
+    <t>Jawaban bener</t>
+  </si>
+  <si>
+    <t>2 (Kode Produk n No Faktur)</t>
+  </si>
+  <si>
+    <t>Kode Faktur --&gt; Partial Dependency yg menentukan Pelanggan dan Tanggal
+Kode Produk --&gt; Partial ke ID Produk dan Kode Kategori</t>
+  </si>
+  <si>
+    <t>Jika menjadi 4 PK</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (FK)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (PK)</t>
+  </si>
+  <si>
+    <t>No Faktur (PK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (FK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (PK)</t>
+  </si>
+  <si>
+    <t>No Faktur --&gt; Tanggal, Kode pelanggan, Total Faktur
+Kode produk --&gt; Nama produk, Harga Satuan
+Kode Kategori --&gt; Nama Kategori
+Kode Pelanggan --&gt; Nama Pelanggan, email, kota</t>
+  </si>
+  <si>
+    <t>No Faktur, Kode Produk, Kode Kategori, Kode Pelanggan</t>
+  </si>
+  <si>
+    <t>Menghilangkan duplikasi / redudansi data</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>No Faktur (PK) (FK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK) (FK)</t>
   </si>
 </sst>
 </file>
@@ -569,9 +673,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,8 +761,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -696,8 +812,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -720,11 +842,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -742,7 +873,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -752,11 +883,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -772,6 +902,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1205,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1519,7 +1661,7 @@
         <v>4450000</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>107</v>
       </c>
@@ -1527,7 +1669,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>100</v>
       </c>
@@ -1535,32 +1677,31 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:1" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:1" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:1" s="20" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
@@ -1574,16 +1715,16 @@
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="30" style="22" customWidth="1"/>
+    <col min="3" max="3" width="30" style="21" customWidth="1"/>
     <col min="4" max="4" width="19.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="22"/>
+    <col min="7" max="7" width="9.140625" style="21"/>
     <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="22" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="21" customWidth="1"/>
     <col min="10" max="10" width="17.42578125" customWidth="1"/>
     <col min="12" max="12" width="17.42578125" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
@@ -1605,16 +1746,22 @@
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="E5" s="27" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>91</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -1624,15 +1771,18 @@
       <c r="B7" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>93</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1651,7 +1801,7 @@
       <c r="B12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="23" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="11" t="s">
@@ -1663,13 +1813,13 @@
       <c r="F12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="23" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="23" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="11" t="s">
@@ -1686,13 +1836,13 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="13">
         <v>46266</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="12" t="s">
@@ -1704,13 +1854,13 @@
       <c r="F13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="24" t="s">
         <v>109</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="24" t="s">
         <v>111</v>
       </c>
       <c r="J13" s="12" t="s">
@@ -1727,13 +1877,13 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="13">
         <v>46266</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D14" s="12" t="s">
@@ -1745,13 +1895,13 @@
       <c r="F14" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="24" t="s">
         <v>117</v>
       </c>
       <c r="J14" s="12" t="s">
@@ -1768,13 +1918,13 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="13">
         <v>46275</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="12" t="s">
@@ -1786,13 +1936,13 @@
       <c r="F15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="I15" s="24" t="s">
         <v>117</v>
       </c>
       <c r="J15" s="12" t="s">
@@ -1809,13 +1959,13 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="13">
         <v>46275</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D16" s="12" t="s">
@@ -1827,13 +1977,13 @@
       <c r="F16" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="24" t="s">
         <v>122</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="24" t="s">
         <v>117</v>
       </c>
       <c r="J16" s="12" t="s">
@@ -1850,13 +2000,13 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>57</v>
       </c>
       <c r="B17" s="13">
         <v>46277</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="24" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1868,13 +2018,13 @@
       <c r="F17" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="24" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="24" t="s">
         <v>64</v>
       </c>
       <c r="J17" s="12" t="s">
@@ -1891,13 +2041,13 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="13">
         <v>46280</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="12" t="s">
@@ -1909,13 +2059,13 @@
       <c r="F18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="I18" s="24" t="s">
         <v>125</v>
       </c>
       <c r="J18" s="12" t="s">
@@ -1932,13 +2082,13 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="25" t="s">
         <v>68</v>
       </c>
       <c r="B19" s="13">
         <v>46280</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D19" s="12" t="s">
@@ -1950,13 +2100,13 @@
       <c r="F19" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="I19" s="25" t="s">
+      <c r="I19" s="24" t="s">
         <v>128</v>
       </c>
       <c r="J19" s="12" t="s">
@@ -1973,13 +2123,13 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="13">
         <v>46283</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="12" t="s">
@@ -1991,13 +2141,13 @@
       <c r="F20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="24" t="s">
         <v>131</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="I20" s="25" t="s">
+      <c r="I20" s="24" t="s">
         <v>111</v>
       </c>
       <c r="J20" s="12" t="s">
@@ -2014,13 +2164,13 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>75</v>
       </c>
       <c r="B21" s="13">
         <v>46283</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="12" t="s">
@@ -2032,13 +2182,13 @@
       <c r="F21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="I21" s="25" t="s">
+      <c r="I21" s="24" t="s">
         <v>125</v>
       </c>
       <c r="J21" s="12" t="s">
@@ -2055,13 +2205,13 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="25" t="s">
         <v>75</v>
       </c>
       <c r="B22" s="13">
         <v>46283</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D22" s="12" t="s">
@@ -2073,13 +2223,13 @@
       <c r="F22" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="I22" s="25" t="s">
+      <c r="I22" s="24" t="s">
         <v>125</v>
       </c>
       <c r="J22" s="12" t="s">
@@ -2096,13 +2246,13 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="25" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="13">
         <v>46285</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="24" t="s">
         <v>58</v>
       </c>
       <c r="D23" s="12" t="s">
@@ -2114,13 +2264,13 @@
       <c r="F23" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="24" t="s">
         <v>109</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I23" s="25" t="s">
+      <c r="I23" s="24" t="s">
         <v>111</v>
       </c>
       <c r="J23" s="12" t="s">
@@ -2137,13 +2287,13 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="25" t="s">
         <v>82</v>
       </c>
       <c r="B24" s="13">
         <v>46285</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="24" t="s">
         <v>58</v>
       </c>
       <c r="D24" s="12" t="s">
@@ -2155,13 +2305,13 @@
       <c r="F24" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="24" t="s">
         <v>122</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="25" t="s">
+      <c r="I24" s="24" t="s">
         <v>117</v>
       </c>
       <c r="J24" s="12" t="s">
@@ -2185,73 +2335,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2316,4 +2399,690 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:U42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.42578125" customWidth="1"/>
+    <col min="2" max="2" width="62.140625" customWidth="1"/>
+    <col min="3" max="3" width="30" style="29" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="29"/>
+    <col min="10" max="10" width="17.5703125" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" customWidth="1"/>
+    <col min="14" max="14" width="25.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" customWidth="1"/>
+    <col min="18" max="19" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="M11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="M12" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="M13" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="13">
+        <v>46266</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="P13" s="14">
+        <v>2150000</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="M14" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="13">
+        <v>46275</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="P14" s="14">
+        <v>900000</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="T14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="M15" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="13">
+        <v>46277</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="P15" s="14">
+        <v>1050000</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="S15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="T15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="25"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="M16" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="N16" s="13">
+        <v>46280</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16" s="14">
+        <v>346000</v>
+      </c>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+    </row>
+    <row r="17" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="M17" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="N17" s="13">
+        <v>46283</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="P17" s="14">
+        <v>548000</v>
+      </c>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+    </row>
+    <row r="18" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="25"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="M18" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="N18" s="13">
+        <v>46285</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="P18" s="14">
+        <v>4450000</v>
+      </c>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+    </row>
+    <row r="21" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="23"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="M21" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="24"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="M22" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="P22" s="14">
+        <v>1850000</v>
+      </c>
+      <c r="S22" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="T22" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="24"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="M23" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="S23" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="T23" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="24"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="M24" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P24" s="14">
+        <v>25000</v>
+      </c>
+      <c r="S24" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="T24" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="24"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="M25" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" s="14">
+        <v>48000</v>
+      </c>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="14"/>
+      <c r="M26" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="P26" s="14">
+        <v>150000</v>
+      </c>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+    </row>
+    <row r="27" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="14"/>
+      <c r="M27" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="14"/>
+    </row>
+    <row r="30" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="M30" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="N30" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="O30" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+    </row>
+    <row r="31" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="14"/>
+      <c r="M31" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="N31" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="O31" s="12">
+        <v>1</v>
+      </c>
+      <c r="P31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="M32" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="N32" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="M33" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="N33" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="O33" s="12">
+        <v>1</v>
+      </c>
+      <c r="P33" s="14"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="12"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="14"/>
+      <c r="M34" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="N34" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="O34" s="12">
+        <v>1</v>
+      </c>
+      <c r="P34" s="12"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="12"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" s="24"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="M35" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="O35" s="12">
+        <v>3</v>
+      </c>
+      <c r="P35" s="14"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="12"/>
+    </row>
+    <row r="36" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="M36" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="N36" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="O36" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M37" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="N37" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="O37" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M38" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="N38" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="O38" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="M39" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="N39" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="O39" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M40" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="N40" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="O40" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="M41" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="N41" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="O41" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M42" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="N42" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="O42" s="32">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Normalisasi_SalesDB_Muaafii.xlsx
+++ b/Normalisasi_SalesDB_Muaafii.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muaafii Putra R\Documents\Kerja\MII-Maganghub\github\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5157BF-EAE1-4E69-AFB7-ED1D52C435BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0F1666-629B-4AC8-A1A9-A506E42E4EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
     <sheet name="1_UNF" sheetId="2" r:id="rId2"/>
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
-    <sheet name="4_3NF" sheetId="5" r:id="rId4"/>
-    <sheet name="3_2NF" sheetId="4" r:id="rId5"/>
+    <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
+    <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -137,8 +137,32 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{416A332B-BA4C-45C8-A3CC-1D55BF3B4CB0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="157">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -774,7 +798,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -818,6 +842,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -855,7 +885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -913,6 +943,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2335,73 +2374,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3085,4 +3057,500 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="16"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="14">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="14">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="14">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="14">
+        <v>4450000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="14">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="14">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="14">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="32">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Normalisasi_SalesDB_Muaafii.xlsx
+++ b/Normalisasi_SalesDB_Muaafii.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muaafii Putra R\Documents\Kerja\MII-Maganghub\github\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0F1666-629B-4AC8-A1A9-A506E42E4EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92E1141-893B-4264-B36E-712030AEC289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
+    <sheet name="Diagram" sheetId="6" r:id="rId6"/>
+    <sheet name="Script" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -162,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="237">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -690,6 +692,7098 @@
   </si>
   <si>
     <t>Kode Produk (PK) (FK)</t>
+  </si>
+  <si>
+    <t>ERD Diagram SalesDB</t>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATABASE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> SalesDB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <r>
+      <t>USE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> SalesDB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> @uuid </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> @uuid </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> GENERATEDUUID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWSEQUENTIALID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Email </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UQ_CustomerEmail </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        City </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CategoryName </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        SubCategoryKey </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_SubCategoryKey </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Invoice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        InvoiceID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWSEQUENTIALID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Invoice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATETIME2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWSEQUENTIALID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>));</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        ProductName </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">CHECK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_ProductCategory </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>));</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> InvoiceDetail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    InvoiceID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Quantity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CK_InvoiceDetail_Quantity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">CHECK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Quantity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    UnitPrice_At_Sale </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    TotalPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">AS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Quantity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice_At_Sale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_InvoiceDetail </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>InvoiceID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_InvoiceDetail_Invoice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>InvoiceID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Invoice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>InvoiceID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_InvoiceDetail_Product </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>));</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> City</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>VALUES</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Budi Santoso'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'budi@gmail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Jakarta'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Siti Aminah'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'siti@gmail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Bandung'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Andi Wijaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'andi@gmail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Surabaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CategoryName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>VALUES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Elektronik'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Alat Tulis'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Aksesoris Komputer'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>VALUES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Monitor 24 Inci'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'1850000.00'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'98'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Headset USB'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'350000.00'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'99'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Buku Catatan A5'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'25000.00'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'99'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Pulpen Gel (Isi 12)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'48000.00'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'99'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Mouse Wireless'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'150000.00'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'99'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Keyboard Mekanik'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'750000.00'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'99'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Invoice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>VALUES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>((</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Budi Santoso'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-01'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>((</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Siti Aminah'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-10'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>((</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Andi Wijaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-12'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>((</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Budi Santoso'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-15'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>((</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Siti Aminah'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-18'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>((</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Andi Wijaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-20'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> InvoiceDetail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>InvoiceID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice_At_Sale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>VALUES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> InvoiceID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Invoice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Budi Santoso'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-01'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                1850000.00</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                150000.00</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> InvoiceID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Invoice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Siti Aminah'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-10'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                750000.00</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> InvoiceID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Invoice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Andi Wijaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-12'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                350000.00</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> InvoiceID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Invoice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Budi Santoso'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-15'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                25000.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                48000.00</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> InvoiceDetail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Invoice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>SCRIPT SQL SERVER</t>
+  </si>
+  <si>
+    <t>SETUP DATABASE SALESDB</t>
   </si>
 </sst>
 </file>
@@ -699,7 +7793,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -797,6 +7891,36 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -885,7 +8009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -934,15 +8058,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -953,6 +8075,15 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -969,6 +8100,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{138943FF-C685-5D9A-6AEC-244B003ABE5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="66675" y="1095375"/>
+          <a:ext cx="11058525" cy="4391025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1813,7 +9010,7 @@
       <c r="C7" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="27" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2380,12 +9577,11 @@
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
     <col min="2" max="2" width="62.140625" customWidth="1"/>
-    <col min="3" max="3" width="30" style="29" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" customWidth="1"/>
     <col min="7" max="7" width="24.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="29"/>
     <col min="10" max="10" width="17.5703125" customWidth="1"/>
     <col min="12" max="12" width="13.85546875" customWidth="1"/>
     <col min="13" max="13" width="18.5703125" customWidth="1"/>
@@ -2860,13 +10056,13 @@
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="M30" s="30" t="s">
+      <c r="M30" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="N30" s="30" t="s">
+      <c r="N30" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="O30" s="30" t="s">
+      <c r="O30" s="28" t="s">
         <v>154</v>
       </c>
       <c r="S30" s="12"/>
@@ -2880,10 +10076,10 @@
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
       <c r="G31" s="14"/>
-      <c r="M31" s="31" t="s">
+      <c r="M31" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="N31" s="31" t="s">
+      <c r="N31" s="29" t="s">
         <v>109</v>
       </c>
       <c r="O31" s="12">
@@ -2901,10 +10097,10 @@
       <c r="E32" s="12"/>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
-      <c r="M32" s="31" t="s">
+      <c r="M32" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="N32" s="31" t="s">
+      <c r="N32" s="29" t="s">
         <v>116</v>
       </c>
       <c r="O32">
@@ -2921,10 +10117,10 @@
       <c r="E33" s="12"/>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
-      <c r="M33" s="31" t="s">
+      <c r="M33" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="N33" s="31" t="s">
+      <c r="N33" s="29" t="s">
         <v>116</v>
       </c>
       <c r="O33" s="12">
@@ -2942,10 +10138,10 @@
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="14"/>
-      <c r="M34" s="31" t="s">
+      <c r="M34" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="N34" s="31" t="s">
+      <c r="N34" s="29" t="s">
         <v>122</v>
       </c>
       <c r="O34" s="12">
@@ -2963,10 +10159,10 @@
       <c r="E35" s="12"/>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
-      <c r="M35" s="31" t="s">
+      <c r="M35" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="N35" s="31" t="s">
+      <c r="N35" s="29" t="s">
         <v>62</v>
       </c>
       <c r="O35" s="12">
@@ -2977,79 +10173,79 @@
       <c r="T35" s="12"/>
     </row>
     <row r="36" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="M36" s="31" t="s">
+      <c r="M36" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="N36" s="31" t="s">
+      <c r="N36" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="O36" s="32">
+      <c r="O36" s="30">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M37" s="31" t="s">
+      <c r="M37" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="N37" s="31" t="s">
+      <c r="N37" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="O37" s="32">
+      <c r="O37" s="30">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M38" s="31" t="s">
+      <c r="M38" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="N38" s="31" t="s">
+      <c r="N38" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="M39" s="31" t="s">
+      <c r="M39" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="N39" s="31" t="s">
+      <c r="N39" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="30">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M40" s="31" t="s">
+      <c r="M40" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="N40" s="31" t="s">
+      <c r="N40" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="O40" s="32">
+      <c r="O40" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="M41" s="31" t="s">
+      <c r="M41" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="N41" s="31" t="s">
+      <c r="N41" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="30">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="M42" s="31" t="s">
+      <c r="M42" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="N42" s="31" t="s">
+      <c r="N42" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="30">
         <v>1</v>
       </c>
     </row>
@@ -3137,7 +10333,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="31" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
@@ -3151,7 +10347,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="31" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -3165,7 +10361,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="31" t="s">
         <v>58</v>
       </c>
       <c r="B15" s="12" t="s">
@@ -3193,7 +10389,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="32" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="13">
@@ -3207,7 +10403,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="32" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="13">
@@ -3221,7 +10417,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="32" t="s">
         <v>57</v>
       </c>
       <c r="B20" s="13">
@@ -3235,7 +10431,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="32" t="s">
         <v>68</v>
       </c>
       <c r="B21" s="13">
@@ -3249,7 +10445,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="32" t="s">
         <v>75</v>
       </c>
       <c r="B22" s="13">
@@ -3263,7 +10459,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="32" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="13">
@@ -3291,7 +10487,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="32" t="s">
         <v>109</v>
       </c>
       <c r="B26" s="12" t="s">
@@ -3305,7 +10501,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="32" t="s">
         <v>62</v>
       </c>
       <c r="B27" s="12" t="s">
@@ -3319,7 +10515,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="32" t="s">
         <v>123</v>
       </c>
       <c r="B28" s="12" t="s">
@@ -3333,7 +10529,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="32" t="s">
         <v>130</v>
       </c>
       <c r="B29" s="12" t="s">
@@ -3347,7 +10543,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="32" t="s">
         <v>116</v>
       </c>
       <c r="B30" s="12" t="s">
@@ -3361,7 +10557,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="34" t="s">
+      <c r="A31" s="32" t="s">
         <v>122</v>
       </c>
       <c r="B31" s="12" t="s">
@@ -3383,7 +10579,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
+      <c r="A34" s="31" t="s">
         <v>111</v>
       </c>
       <c r="B34" s="12" t="s">
@@ -3391,7 +10587,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="31" t="s">
         <v>125</v>
       </c>
       <c r="B35" s="12" t="s">
@@ -3399,7 +10595,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="33" t="s">
+      <c r="A36" s="31" t="s">
         <v>117</v>
       </c>
       <c r="B36" s="12" t="s">
@@ -3407,21 +10603,21 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="28" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="35" t="s">
+      <c r="B39" s="33" t="s">
         <v>109</v>
       </c>
       <c r="C39" s="12">
@@ -3429,10 +10625,10 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="35" t="s">
+      <c r="A40" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="33" t="s">
         <v>116</v>
       </c>
       <c r="C40">
@@ -3440,10 +10636,10 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="35" t="s">
+      <c r="A41" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="35" t="s">
+      <c r="B41" s="33" t="s">
         <v>116</v>
       </c>
       <c r="C41" s="12">
@@ -3451,10 +10647,10 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="35" t="s">
+      <c r="B42" s="33" t="s">
         <v>122</v>
       </c>
       <c r="C42" s="12">
@@ -3462,10 +10658,10 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="35" t="s">
+      <c r="A43" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="33" t="s">
         <v>62</v>
       </c>
       <c r="C43" s="12">
@@ -3473,79 +10669,79 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="30">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="35" t="s">
+      <c r="A45" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="35" t="s">
+      <c r="B45" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="30">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B47" s="35" t="s">
+      <c r="B47" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="30">
         <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="35" t="s">
+      <c r="A48" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="35" t="s">
+      <c r="A49" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="B49" s="35" t="s">
+      <c r="B49" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="30">
         <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="35" t="s">
+      <c r="A50" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="30">
         <v>1</v>
       </c>
     </row>
@@ -3553,4 +10749,827 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DFE41C-BA65-4357-8CC3-394278298EF6}">
+  <dimension ref="B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0321AA3-03A4-4A60-8AA3-514CF008BFD3}">
+  <dimension ref="A1:A167"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="35"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="35"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="35"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="35"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="35"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="34" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="35"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="36" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="35"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="34" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="36" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="36" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="36" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="36" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="35"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="34" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="34" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="35"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="34" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="35"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="34" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="34" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="34" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="34" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="34" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="34" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="34" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="35"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="34" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="34" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="34" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="34" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="34" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="35"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="36" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="36" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="36" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="36" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="34" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="36" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="36" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="36" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="36" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="36" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="36" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="34" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="36" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="34" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="36" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="35"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="34" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="35"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="34" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="34" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="34" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="34" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="34" t="s">
+        <v>234</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>